--- a/308. ВГК№5 (Балчуг) v.2 копия.xlsx
+++ b/308. ВГК№5 (Балчуг) v.2 копия.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pto47\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADAA9617-0C81-49ED-8906-E2CDE2697D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF277CB2-59BA-47E5-8DE8-53A5C3929CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="225" windowWidth="28770" windowHeight="15450" xr2:uid="{0885596A-FD4C-4ADE-AC12-F9B536577640}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="89">
   <si>
     <t>№ этажа</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>Разводка попутного типа</t>
+  </si>
+  <si>
+    <t>Толщина изоляции 13мм</t>
   </si>
 </sst>
 </file>
@@ -4704,7 +4707,10 @@
       </c>
       <c r="J80" s="94"/>
     </row>
-    <row r="81" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C81" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="G81" s="94">
         <v>1850</v>
       </c>
@@ -4717,7 +4723,7 @@
       </c>
       <c r="J81" s="94"/>
     </row>
-    <row r="82" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:10" x14ac:dyDescent="0.25">
       <c r="G82" s="94">
         <v>2200</v>
       </c>
@@ -4727,7 +4733,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="83" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:10" x14ac:dyDescent="0.25">
       <c r="G83" s="94">
         <v>3040</v>
       </c>
@@ -4737,7 +4743,7 @@
       </c>
       <c r="J83" s="94"/>
     </row>
-    <row r="84" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
       <c r="G84" s="94">
         <v>840</v>
       </c>
@@ -4749,7 +4755,7 @@
       </c>
       <c r="J84" s="94"/>
     </row>
-    <row r="85" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:10" x14ac:dyDescent="0.25">
       <c r="G85" s="94" t="s">
         <v>72</v>
       </c>
@@ -4761,13 +4767,13 @@
         <v>63</v>
       </c>
     </row>
-    <row r="86" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
       <c r="G86" s="94"/>
       <c r="H86" s="94"/>
       <c r="I86" s="94"/>
       <c r="J86" s="94"/>
     </row>
-    <row r="87" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
       <c r="G87" s="94" t="s">
         <v>78</v>
       </c>
